--- a/02_ai-risk-framework-implementation-nist-ai-rmf/exercises/solution/risk_assessment.xlsx
+++ b/02_ai-risk-framework-implementation-nist-ai-rmf/exercises/solution/risk_assessment.xlsx
@@ -594,7 +594,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>- EU AI Act: FraudShield classified as High-Risk for credit and fraud decisions</t>
+          <t>- EU AI Act: fraud-detection is exempt from Annex III 5(b) High-Risk classification; FraudShield is governed as High-Risk internally because its outputs can feed credit-limit and account-eligibility decisions</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Identify all risks across NIST AI RMF categories (technical, ethical, legal, operational), populate the risk register with mitigation strategies, score risks, and generate an executive summary.</t>
+          <t>Identify all risks across the four risk categories (technical, ethical, legal, operational), map each to a NIST AI RMF function (Govern / Map / Measure / Manage), populate the risk register with mitigation strategies, score risks, and generate an executive summary.</t>
         </is>
       </c>
     </row>

--- a/02_ai-risk-framework-implementation-nist-ai-rmf/exercises/solution/risk_assessment.xlsx
+++ b/02_ai-risk-framework-implementation-nist-ai-rmf/exercises/solution/risk_assessment.xlsx
@@ -2300,7 +2300,7 @@
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>"15"
-Reasoning: This count should match the risk register rows. Cross-referencing validates completeness.</t>
+Reasoning: The summary covers the 15 base risks (R001-R015). R016-R018 are the GenAI-specific rows students add; they are tracked in the register but not in this summary.</t>
         </is>
       </c>
     </row>
@@ -2338,8 +2338,8 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>"5"
-Reasoning: R009-R011, R014-R015. Scores 5-9. Plan within 90 days.</t>
+          <t>"3"
+Reasoning: R009, R010, R015. Scores 5-9. Plan within 90 days.</t>
         </is>
       </c>
     </row>
@@ -2351,8 +2351,8 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>"0"
-Reasoning: No risks scored below 5. This is expected for a high-risk fintech AI system — all identified risks have meaningful impact.</t>
+          <t>"2"
+Reasoning: R011 and R014 score 4 (&lt;5). The workbook register scores both at impact 2; the notebook scoring pass reads them at 3 - see the calibration note in the README.</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
